--- a/autoprogram/vgpio/address mapper.xlsx
+++ b/autoprogram/vgpio/address mapper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\vgpio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F90501A-BCFE-4D0A-A46E-B9A07F57DCBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CE7688-34BA-457A-849D-BB44512FE034}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
@@ -302,67 +302,7 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>

--- a/autoprogram/vgpio/address mapper.xlsx
+++ b/autoprogram/vgpio/address mapper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\vgpio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CE7688-34BA-457A-849D-BB44512FE034}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B22A274-A7BA-4896-AFDF-FB03A16679F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
